--- a/design_issues/codescene/P3_Ecommerce.xlsx
+++ b/design_issues/codescene/P3_Ecommerce.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DIinAGP\DIinAGP\design_issues\codescene\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="89">
   <si>
     <t>resource</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Primitive Obsession ()</t>
   </si>
   <si>
-    <t>String Heavy Function Arguments</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments ()</t>
-  </si>
-  <si>
     <t>Excess Number of Function Arguments</t>
   </si>
   <si>
@@ -67,12 +61,6 @@
     <t>Excess Number of Function Arguments (Arguments = 6)</t>
   </si>
   <si>
-    <t>Constructor Over-Injection</t>
-  </si>
-  <si>
-    <t>Constructor Over-Injection ()</t>
-  </si>
-  <si>
     <t>Complex Method</t>
   </si>
   <si>
@@ -209,12 +197,6 @@
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P3_Ecommerce/backend/src/main/java/com/ecommerce/dto/StripeWebhookEvent.java</t>
-  </si>
-  <si>
-    <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P3_Ecommerce/backend/src/main/java/com/ecommerce/model/Order.java</t>
-  </si>
-  <si>
-    <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P3_Ecommerce/backend/src/main/java/com/ecommerce/model/OrderItem.java</t>
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/P3_Ecommerce/backend/src/main/java/com/ecommerce/model/Product.java</t>
@@ -682,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="113.90625" customWidth="1"/>
@@ -711,7 +693,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -728,7 +710,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -745,7 +727,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -762,7 +744,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -779,7 +761,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -796,7 +778,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -813,7 +795,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -830,7 +812,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -847,24 +829,24 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
@@ -873,15 +855,15 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E11">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -890,66 +872,66 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E12">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="E13">
-        <v>79</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
       <c r="D14">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E14">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="E15">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -958,15 +940,15 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="E16">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -975,15 +957,15 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E17">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
@@ -992,15 +974,15 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="E18">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
@@ -1009,15 +991,15 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="E19">
-        <v>219</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
@@ -1026,15 +1008,15 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E20">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
@@ -1043,15 +1025,15 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="E21">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -1060,15 +1042,15 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="E22">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
@@ -1077,15 +1059,15 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="E23">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
@@ -1094,15 +1076,15 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>330</v>
+        <v>384</v>
       </c>
       <c r="E24">
-        <v>330</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
@@ -1111,15 +1093,15 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>384</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>384</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
@@ -1128,15 +1110,15 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E26">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
@@ -1145,15 +1127,15 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E27">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
@@ -1162,72 +1144,72 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="E28">
-        <v>79</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31">
         <v>50</v>
       </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31">
-        <v>39</v>
-      </c>
       <c r="E31">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>50</v>
@@ -1238,30 +1220,30 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E33">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>62</v>
@@ -1272,30 +1254,30 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E35">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D36">
         <v>74</v>
@@ -1306,24 +1288,24 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="E37">
-        <v>74</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
@@ -1332,32 +1314,32 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E38">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D39">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>118</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
@@ -1374,13 +1356,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1391,7 +1373,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -1408,13 +1390,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1425,7 +1407,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
@@ -1442,13 +1424,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1479,10 +1461,10 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1493,7 +1475,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
         <v>7</v>
@@ -1510,13 +1492,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1527,7 +1509,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
@@ -1544,13 +1526,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1561,7 +1543,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
         <v>7</v>
@@ -1578,13 +1560,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1595,41 +1577,41 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
@@ -1646,155 +1628,155 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>533</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>533</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>218</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -1802,16 +1784,16 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -1836,38 +1818,38 @@
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -1876,112 +1858,112 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D72">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="E72">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D73">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="E73">
-        <v>133</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D75">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="E75">
-        <v>65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C76" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76">
         <v>19</v>
       </c>
-      <c r="D76">
-        <v>391</v>
-      </c>
       <c r="E76">
-        <v>391</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -1989,16 +1971,16 @@
         <v>69</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D77">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="E77">
-        <v>391</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -2006,16 +1988,16 @@
         <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D78">
-        <v>533</v>
+        <v>18</v>
       </c>
       <c r="E78">
-        <v>533</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -2023,16 +2005,16 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D79">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="E79">
-        <v>96</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
@@ -2040,480 +2022,480 @@
         <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D80">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="E80">
-        <v>122</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D81">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="E81">
-        <v>145</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D82">
-        <v>218</v>
+        <v>6</v>
       </c>
       <c r="E82">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D83">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="E83">
-        <v>240</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C84" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D84">
-        <v>262</v>
+        <v>17</v>
       </c>
       <c r="E84">
-        <v>262</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B85" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C86" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D86">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E86">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C87" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D87">
-        <v>63</v>
+        <v>209</v>
       </c>
       <c r="E87">
-        <v>63</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D88">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="E88">
-        <v>113</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D89">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E89">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D90">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>135</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B91" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D91">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="E91">
-        <v>17</v>
+        <v>165</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D92">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="E92">
-        <v>17</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E93">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B94" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D94">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E94">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B95" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D95">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D96">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E96">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D97">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="E97">
-        <v>45</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C98" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D98">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="E98">
-        <v>45</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D99">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E99">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E100">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D101">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E101">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D102">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E102">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B103" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D103">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="E103">
-        <v>64</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C104" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D104">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E104">
-        <v>67</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B105" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C105" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D105">
-        <v>209</v>
+        <v>93</v>
       </c>
       <c r="E105">
-        <v>209</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C106" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D106">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E106">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B107" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D107">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="E107">
-        <v>143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
@@ -2530,13 +2512,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -2547,426 +2529,86 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B110" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D110">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="E110">
-        <v>165</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B111" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D111">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="E111">
-        <v>185</v>
+        <v>71</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D112">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E112">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C113" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D113">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="E113">
-        <v>13</v>
+        <v>108</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B114" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D114">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="E114">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>83</v>
-      </c>
-      <c r="B115" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" t="s">
-        <v>40</v>
-      </c>
-      <c r="D115">
-        <v>19</v>
-      </c>
-      <c r="E115">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>83</v>
-      </c>
-      <c r="B116" t="s">
-        <v>35</v>
-      </c>
-      <c r="C116" t="s">
-        <v>36</v>
-      </c>
-      <c r="D116">
-        <v>204</v>
-      </c>
-      <c r="E116">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>83</v>
-      </c>
-      <c r="B117" t="s">
-        <v>35</v>
-      </c>
-      <c r="C117" t="s">
-        <v>36</v>
-      </c>
-      <c r="D117">
-        <v>209</v>
-      </c>
-      <c r="E117">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>84</v>
-      </c>
-      <c r="B118" t="s">
-        <v>17</v>
-      </c>
-      <c r="C118" t="s">
-        <v>41</v>
-      </c>
-      <c r="D118">
-        <v>14</v>
-      </c>
-      <c r="E118">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>84</v>
-      </c>
-      <c r="B119" t="s">
-        <v>23</v>
-      </c>
-      <c r="C119" t="s">
-        <v>42</v>
-      </c>
-      <c r="D119">
-        <v>14</v>
-      </c>
-      <c r="E119">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>85</v>
-      </c>
-      <c r="B120" t="s">
-        <v>17</v>
-      </c>
-      <c r="C120" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120">
-        <v>19</v>
-      </c>
-      <c r="E120">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>85</v>
-      </c>
-      <c r="B121" t="s">
-        <v>23</v>
-      </c>
-      <c r="C121" t="s">
-        <v>44</v>
-      </c>
-      <c r="D121">
-        <v>19</v>
-      </c>
-      <c r="E121">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>86</v>
-      </c>
-      <c r="B122" t="s">
-        <v>17</v>
-      </c>
-      <c r="C122" t="s">
-        <v>41</v>
-      </c>
-      <c r="D122">
-        <v>18</v>
-      </c>
-      <c r="E122">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>86</v>
-      </c>
-      <c r="B123" t="s">
-        <v>23</v>
-      </c>
-      <c r="C123" t="s">
-        <v>45</v>
-      </c>
-      <c r="D123">
-        <v>18</v>
-      </c>
-      <c r="E123">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>86</v>
-      </c>
-      <c r="B124" t="s">
-        <v>35</v>
-      </c>
-      <c r="C124" t="s">
-        <v>36</v>
-      </c>
-      <c r="D124">
-        <v>93</v>
-      </c>
-      <c r="E124">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>87</v>
-      </c>
-      <c r="B125" t="s">
-        <v>23</v>
-      </c>
-      <c r="C125" t="s">
-        <v>46</v>
-      </c>
-      <c r="D125">
-        <v>5</v>
-      </c>
-      <c r="E125">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>88</v>
-      </c>
-      <c r="B126" t="s">
-        <v>7</v>
-      </c>
-      <c r="C126" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126">
-        <v>1</v>
-      </c>
-      <c r="E126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>89</v>
-      </c>
-      <c r="B127" t="s">
-        <v>7</v>
-      </c>
-      <c r="C127" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>89</v>
-      </c>
-      <c r="B128" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" t="s">
-        <v>10</v>
-      </c>
-      <c r="D128">
-        <v>1</v>
-      </c>
-      <c r="E128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>90</v>
-      </c>
-      <c r="B129" t="s">
-        <v>7</v>
-      </c>
-      <c r="C129" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>90</v>
-      </c>
-      <c r="B130" t="s">
-        <v>11</v>
-      </c>
-      <c r="C130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D130">
-        <v>64</v>
-      </c>
-      <c r="E130">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>90</v>
-      </c>
-      <c r="B131" t="s">
-        <v>11</v>
-      </c>
-      <c r="C131" t="s">
-        <v>12</v>
-      </c>
-      <c r="D131">
-        <v>71</v>
-      </c>
-      <c r="E131">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>90</v>
-      </c>
-      <c r="B132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132" t="s">
-        <v>14</v>
-      </c>
-      <c r="D132">
-        <v>78</v>
-      </c>
-      <c r="E132">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>90</v>
-      </c>
-      <c r="B133" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" t="s">
-        <v>6</v>
-      </c>
-      <c r="D133">
-        <v>108</v>
-      </c>
-      <c r="E133">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>90</v>
-      </c>
-      <c r="B134" t="s">
-        <v>5</v>
-      </c>
-      <c r="C134" t="s">
-        <v>6</v>
-      </c>
-      <c r="D134">
-        <v>129</v>
-      </c>
-      <c r="E134">
         <v>129</v>
       </c>
     </row>
@@ -2977,7 +2619,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:C11"/>
+  <dimension ref="A2:C9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="34.08984375" customWidth="1"/>
@@ -2986,13 +2628,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -3003,7 +2645,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIF(Issues!B2:B135,B3)</f>
+        <f>COUNTIF(Issues!B2:B115,B3)</f>
         <v>44</v>
       </c>
     </row>
@@ -3015,7 +2657,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIF(Issues!B2:B135,B4)</f>
+        <f>COUNTIF(Issues!B2:B115,B4)</f>
         <v>23</v>
       </c>
     </row>
@@ -3024,10 +2666,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIF(Issues!B2:B135,B5)</f>
+        <f>COUNTIF(Issues!B2:B115,B5)</f>
         <v>12</v>
       </c>
     </row>
@@ -3036,11 +2678,11 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIF(Issues!B2:B135,B6)</f>
-        <v>9</v>
+        <f>COUNTIF(Issues!B2:B115,B6)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -3048,11 +2690,11 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIF(Issues!B2:B135,B7)</f>
-        <v>11</v>
+        <f>COUNTIF(Issues!B2:B115,B7)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -3060,45 +2702,21 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIF(Issues!B2:B135,B8)</f>
-        <v>16</v>
+        <f>COUNTIF(Issues!B2:B115,B8)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2">
-        <f>COUNTIF(Issues!B2:B135,B9)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="2">
-        <f>COUNTIF(Issues!B2:B135,B10)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="3">
-        <f>SUM(C3:C10)</f>
-        <v>133</v>
+      <c r="A9" s="4"/>
+      <c r="B9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="3">
+        <f>SUM(C3:C8)</f>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
